--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,29 +637,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -756,24 +756,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -880,26 +880,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -907,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +932,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -999,26 +995,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 35分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1026,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1042,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1065,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1113,27 +1105,31 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1141,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1229,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1348,24 +1348,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±10分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路春雅路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1467,24 +1467,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±15分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1556,24 +1556,24 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1586,34 +1586,34 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,47 +1627,880 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:21采样：该车到重点站长岛路台儿庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>6/9</t>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -875,27 +875,31 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 16分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -952,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -990,27 +994,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 35分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1042,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1067,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1224,29 +1232,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1280,12 +1288,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1295,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1351,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路春雅路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1399,12 +1407,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1414,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1472,21 +1480,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1518,12 +1522,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1533,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1586,24 +1590,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1642,7 +1646,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1662,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1700,29 +1704,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站长岛路台儿庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1756,12 +1760,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1781,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1824,24 +1828,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1880,7 +1884,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1900,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1943,24 +1947,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路顾家浜路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1999,7 +2003,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2019,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2062,24 +2066,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2118,7 +2122,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2138,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2181,24 +2185,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±9分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2237,7 +2241,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2257,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2300,24 +2304,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2356,7 +2360,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2376,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2389,24 +2393,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2419,24 +2423,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+          <t>08:11采样：该车到重点站新德西路德川路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2460,47 +2464,757 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>80.5</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>5/13</t>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1470,27 +1470,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 13分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,12 +1526,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1547,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1590,26 +1594,22 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1828,24 +1828,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±9分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1947,19 +1947,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路顾家浜路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2066,24 +2066,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±10分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2185,24 +2185,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2304,19 +2304,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2428,14 +2428,14 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站新德西路德川路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2542,24 +2542,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站博兴路东陆路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2661,24 +2661,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±12分钟</t>
+          <t>08:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3209,12 +3209,250 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1589,27 +1589,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,12 +1645,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1666,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1713,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1823,29 +1827,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1894,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1942,24 +1946,24 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,12 +2002,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2013,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2061,29 +2065,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,12 +2121,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2132,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2180,29 +2184,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,12 +2240,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2251,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2316,7 +2320,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2355,12 +2359,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2370,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2418,29 +2422,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,12 +2478,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2499,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2541,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2547,19 +2551,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站博兴路东陆路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,12 +2597,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2608,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2661,26 +2665,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2780,24 +2780,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±12分钟</t>
+          <t>09:21采样：该车到重点站佳林路金高路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2899,24 +2899,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路创新路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路锦绣东路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3252,19 +3252,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站东陆路金海路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3371,24 +3371,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+          <t>09:21采样：该车到重点站新德西路德翔路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,32 +3427,746 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2546,24 +2546,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2660,27 +2660,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2716,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2727,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2775,29 +2779,29 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站佳林路金高路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2835,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2846,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2894,29 +2898,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路创新路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,12 +2954,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2965,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3013,24 +3017,24 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路锦绣东路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,12 +3073,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3084,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3132,27 +3136,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -3160,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3204,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3247,29 +3255,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站东陆路金海路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3279,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,12 +3311,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3318,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3366,29 +3374,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站新德西路德翔路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3398,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,12 +3430,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3437,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3485,29 +3493,29 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3517,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,12 +3549,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3566,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3604,29 +3612,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3636,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3668,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3685,7 +3693,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3728,26 +3736,22 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 29分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,12 +3783,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3794,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3863,12 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>10:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,12 +3902,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3966,19 +3970,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>10:21采样：该车到重点站唐陆公路川桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4042,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4055,24 +4059,24 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4085,24 +4089,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+          <t>10:21采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,47 +4130,995 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站新川路华东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>80.7</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3741,17 +3741,21 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 29分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,12 +3787,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3808,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3846,29 +3850,29 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,12 +3906,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3917,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3965,29 +3969,29 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站唐陆公路川桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,12 +4025,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4084,24 +4088,24 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4116,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,12 +4144,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4165,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4203,29 +4207,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站新川路华东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4235,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,12 +4263,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4274,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4322,29 +4326,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4354,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,12 +4382,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4403,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4450,26 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>11:21采样：该车到重点站唐陆公路创新路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4469,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,37 +4501,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4556,29 +4564,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4588,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4620,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4627,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4680,24 +4688,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4707,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,7 +4744,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4756,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4799,24 +4807,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>11:21采样：该车到重点站新德西路德翔路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4826,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,7 +4863,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4875,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4918,24 +4926,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>11:21采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4945,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,7 +4982,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4994,7 +5002,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5007,24 +5015,24 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5037,19 +5045,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+          <t>11:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5059,12 +5067,12 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5078,47 +5086,761 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>68分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,17 +4159,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4331,24 +4331,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4445,29 +4445,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站唐陆公路创新路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4569,24 +4569,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4683,29 +4683,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4802,29 +4802,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站新德西路德翔路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4921,29 +4921,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±7分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±6分钟</t>
+          <t>11:41采样：该车到重点站唐陆公路川桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5278,29 +5278,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5402,26 +5402,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5429,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,12 +5449,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5468,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5521,26 +5517,22 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 56分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5548,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5564,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5592,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5763,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>12:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5786,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5815,32 +5807,627 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
+      <c r="Z46" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>79.2</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>9/14</t>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,22 +4516,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5164,24 +5164,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5407,17 +5407,21 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5425,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,12 +5453,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5474,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5512,27 +5516,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 56分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5540,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5572,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5584,17 +5592,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5632,26 +5640,22 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:51采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5687,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5698,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5755,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5763,14 +5767,10 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:51采样，终点ETA 43分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5870,24 +5870,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>12:51采样：该车到重点站荷泽路长岛路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5989,24 +5989,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+          <t>12:51采样：该车到重点站新德西路德川路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,365 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5402,24 +5402,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5635,27 +5635,31 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:51采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -5663,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5691,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5712,12 +5716,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5750,27 +5754,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:51采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -5778,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,12 +5810,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5827,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5865,29 +5873,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:51采样：该车到重点站荷泽路长岛路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5897,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5929,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5946,12 +5954,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5984,29 +5992,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:51采样：该车到重点站新德西路德川路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6048,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6055,22 +6063,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6113,14 +6121,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>13:19采样：该车到重点站唐陆公路锦绣东路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6135,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,7 +6172,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6184,7 +6192,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6227,24 +6235,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+          <t>13:19采样：该车到重点站唐陆公路春雅路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,7 +6291,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6303,12 +6311,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,7 +6430,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6492,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6788,245 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5878,24 +5878,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5997,24 +5997,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6111,29 +6111,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>13:19采样：该车到重点站唐陆公路锦绣东路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6230,24 +6230,24 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13:19采样：该车到重点站唐陆公路春雅路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6349,29 +6349,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6468,29 +6468,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6539,22 +6539,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6587,27 +6587,31 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -6615,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,17 +6643,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6659,17 +6663,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6826,19 +6830,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+          <t>14:21采样：该车到重点站博兴路东陆路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6853,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6886,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6902,12 +6906,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6919,7 @@
       <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -6945,34 +6949,30 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,37 +6996,747 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>43分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>同车下一次反向发车15:20，减去该车自身同类时段历史终点停站中位数17分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X55" s="2" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车反向发车反推</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>67分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,17 +4873,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,22 +5587,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6354,24 +6354,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6473,24 +6473,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6592,24 +6592,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6825,29 +6825,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站博兴路东陆路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6944,27 +6944,31 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>14:01</t>
@@ -6972,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,33 +7000,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7055,29 +7063,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>43分钟</t>
+          <t>45分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车15:20，减去该车自身同类时段历史终点停站中位数17分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7087,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,12 +7119,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7136,12 +7144,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7174,12 +7182,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -7191,12 +7199,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7206,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,12 +7238,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7260,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7301,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -7310,12 +7318,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7357,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7364,22 +7372,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7417,24 +7425,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>57分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±7分钟</t>
+          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7444,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7473,7 +7481,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7483,22 +7491,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7544,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -7548,12 +7556,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±7分钟</t>
+          <t>15:21采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7563,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7592,7 +7600,7 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7612,12 +7620,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7625,24 +7633,24 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7655,24 +7663,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>15:21采样：该车到重点站新川路妙境路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7682,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7696,45 +7704,874 @@
       <c r="T61" s="2" t="inlineStr"/>
       <c r="U61" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>15:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W61" s="2" t="inlineStr">
+      <c r="W62" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X61" s="2" t="inlineStr">
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>1/15</t>
         </is>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,22 +5587,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,17 +6063,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,22 +6420,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,17 +6896,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6949,24 +6949,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,22 +7253,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7306,24 +7306,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7420,29 +7420,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>57分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数23分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7539,29 +7539,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7658,29 +7658,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站新川路妙境路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7729,22 +7729,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7777,29 +7777,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8020,19 +8020,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 37分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8201,22 +8201,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8254,19 +8254,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>16:21采样：该车到重点站德川路华夏东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8373,24 +8373,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8462,24 +8462,24 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A02126A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8492,34 +8492,34 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>16:21采样：该车到重点站新川路华东路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,47 +8533,876 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Y70" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>1/15</t>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5045,19 +5045,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:41采样：该车到重点站唐陆公路川桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+          <t>11:41采样：该车到重点站唐陆公路川桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,17 +5706,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,22 +5944,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,17 +6063,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,17 +6658,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,22 +6777,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,17 +6896,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,17 +7134,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,22 +7372,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,14 +7610,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8015,27 +8015,31 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 37分钟</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>14:01</t>
@@ -8043,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,12 +8071,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8092,12 +8096,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,12 +8215,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8249,29 +8253,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站德川路华夏东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8281,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,12 +8309,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8320,22 +8324,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8368,29 +8372,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8400,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,12 +8428,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8439,22 +8443,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8487,29 +8491,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站新川路华东路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8519,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,12 +8547,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8558,22 +8562,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8606,29 +8610,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8638,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,12 +8666,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8687,12 +8691,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8730,26 +8734,22 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8796,17 +8796,17 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8849,19 +8849,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站佳林路金高路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8968,19 +8968,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路创新路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9044,12 +9044,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9087,24 +9087,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±8分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9206,22 +9206,26 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>17:21采样：该车到重点站唐陆公路春雅路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9229,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9253,17 +9257,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9273,17 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9291,24 +9295,24 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9321,26 +9325,22 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9362,47 +9362,995 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
         <is>
           <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,22 +4516,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,22 +5944,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,22 +6420,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,22 +6539,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,22 +7253,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,22 +7610,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,22 +7729,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,22 +7967,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,22 +8324,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8496,24 +8496,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8729,27 +8729,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8757,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,12 +8785,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8801,12 +8805,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8844,29 +8848,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站佳林路金高路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8876,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,12 +8904,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8915,22 +8919,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8963,29 +8967,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路创新路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8995,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,12 +9023,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9034,22 +9038,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9092,21 +9096,17 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:03采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9153,22 +9153,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9201,29 +9201,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路春雅路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9272,22 +9272,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9320,27 +9320,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9348,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,37 +9376,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9435,29 +9439,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9467,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,12 +9495,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9506,22 +9510,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9554,29 +9558,29 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9586,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,12 +9614,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9635,12 +9639,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9690,12 +9694,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±6分钟</t>
+          <t>同车下一次反向发车19:30，减去该车自身同类时段历史终点停站中位数28分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9705,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9734,7 +9738,7 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9744,22 +9748,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9801,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -9809,14 +9813,10 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:22采样，终点ETA 36分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9916,24 +9916,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±7分钟</t>
+          <t>18:22采样：该车到重点站唐陆公路川桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10035,19 +10035,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+          <t>18:22采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10154,22 +10154,26 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>18:22采样：该车到重点站唐陆公路川桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10177,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10201,17 +10205,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10221,12 +10225,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10239,24 +10243,24 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10269,24 +10273,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>18:22采样：该车到重点站博兴路东陆路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10296,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10325,32 +10329,865 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>18:22采样：该车到重点站新川路华东路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y83" s="2" t="inlineStr">
+      <c r="Y85" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
+      <c r="AA86" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,17 +7134,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9444,24 +9444,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9682,26 +9682,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车19:30，减去该车自身同类时段历史终点停站中位数28分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:32采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9709,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,12 +9729,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9758,7 +9754,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9813,7 +9809,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:22采样，终点ETA 36分钟</t>
+          <t>SHMAAS末次终点ETA推算：18:32采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
@@ -9824,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9863,17 +9859,17 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9943,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10062,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10181,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10300,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10419,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10473,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10657,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10776,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10895,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10944,12 +10940,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11076,24 +11072,24 @@
       <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11106,19 +11102,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11128,12 +11124,12 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11147,45 +11143,164 @@
       <c r="T90" s="2" t="inlineStr"/>
       <c r="U90" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W90" s="2" t="inlineStr">
+      <c r="W91" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X90" s="2" t="inlineStr">
+      <c r="X91" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y90" s="2" t="inlineStr">
+      <c r="Y91" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z90" s="2" t="inlineStr">
+      <c r="Z91" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA90" s="2" t="inlineStr">
+      <c r="AA91" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB90" s="2" t="inlineStr">
-        <is>
-          <t>76.3</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr">
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>5/15</t>
         </is>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,17 +4754,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,17 +6777,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,22 +7372,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,22 +7729,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8443,22 +8443,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8562,22 +8562,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9038,22 +9038,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9563,24 +9563,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -9687,17 +9687,21 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:32采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9705,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,12 +9733,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9754,7 +9758,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9797,19 +9801,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:32采样，终点ETA 26分钟</t>
+          <t>SHMAAS末次终点ETA推算：18:42采样，终点ETA 13分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
@@ -9820,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9844,7 +9848,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
@@ -9869,7 +9873,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9907,29 +9911,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:22采样：该车到重点站唐陆公路川桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±12分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9939,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9963,12 +9967,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9978,22 +9982,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10026,24 +10030,24 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:22采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10058,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,12 +10086,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10097,17 +10101,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10145,29 +10149,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:22采样：该车到重点站唐陆公路川桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10177,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10201,12 +10205,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10226,7 +10230,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10269,26 +10273,22 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:22采样：该车到重点站博兴路东陆路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:22采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10383,24 +10383,24 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:22采样：该车到重点站新川路华东路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10439,12 +10439,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10454,22 +10454,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10507,24 +10507,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±7分钟</t>
+          <t>18:52采样：该车到重点站唐陆公路顾家浜路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10626,26 +10626,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:12采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10653,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10677,12 +10673,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10692,22 +10688,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10745,24 +10741,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+          <t>19:22采样：该车到重点站唐陆公路春雅路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10772,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10801,7 +10797,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10821,7 +10817,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10864,24 +10860,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±8分钟</t>
+          <t>19:22采样：该车到重点站东陆路金海路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10891,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10920,7 +10916,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10940,7 +10936,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10995,12 +10991,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+          <t>19:22采样：该车到重点站新德西路德翔路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11010,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11039,7 +11035,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11102,19 +11098,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>19:22采样：该车到重点站东陆路金海路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11129,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11158,7 +11154,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11178,7 +11174,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11191,24 +11187,24 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11221,19 +11217,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11243,12 +11239,12 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11287,22 +11283,498 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
         <is>
           <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,22 +5944,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,17 +6182,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,22 +7967,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,22 +8324,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8562,17 +8562,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9272,22 +9272,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9748,22 +9748,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9982,17 +9982,17 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10268,12 +10268,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -10285,10 +10285,14 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:22采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10296,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10320,12 +10324,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10350,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10464,12 +10468,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10502,29 +10506,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:52采样：该车到重点站唐陆公路顾家浜路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10534,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10558,12 +10562,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10583,12 +10587,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10621,27 +10625,31 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:12采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10649,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,12 +10681,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10698,12 +10706,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10736,29 +10744,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:22采样：该车到重点站唐陆公路春雅路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10768,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10792,12 +10800,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10817,7 +10825,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10855,29 +10863,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:22采样：该车到重点站东陆路金海路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10887,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10911,12 +10919,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10936,7 +10944,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10974,29 +10982,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:22采样：该车到重点站新德西路德翔路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11006,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,12 +11038,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11045,22 +11053,22 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11093,29 +11101,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:22采样：该车到重点站东陆路金海路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11125,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,12 +11157,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11174,7 +11182,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11217,26 +11225,22 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:23采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11244,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11268,12 +11272,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11293,12 +11297,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11331,29 +11335,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11363,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11387,12 +11391,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11402,22 +11406,22 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11455,24 +11459,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>20:23采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11482,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11511,7 +11515,7 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11531,12 +11535,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11574,26 +11578,22 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:23采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11625,32 +11625,32 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11693,24 +11693,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±12分钟</t>
+          <t>20:23采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11744,37 +11744,394 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>22:27</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-182路.xlsx
+++ b/data/export/2026-09-21-182路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,17 +8567,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,17 +9987,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10706,12 +10706,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11220,27 +11220,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:23采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11248,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11272,12 +11276,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11297,7 +11301,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11367,7 +11371,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11416,12 +11420,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11454,29 +11458,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>20:23采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11486,7 +11490,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11510,12 +11514,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11535,12 +11539,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11573,27 +11577,31 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:23采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11601,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11625,17 +11633,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11645,17 +11653,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11688,24 +11696,24 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>20:23采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11720,7 +11728,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11744,12 +11752,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11769,12 +11777,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11807,29 +11815,29 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11839,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11863,12 +11871,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11888,7 +11896,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11931,26 +11939,22 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:22采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11958,7 +11962,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11982,12 +11986,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -12007,12 +12011,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12050,19 +12054,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>21:22采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -12077,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12106,7 +12110,7 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12121,17 +12125,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
